--- a/backend/data/data wisata.xlsx
+++ b/backend/data/data wisata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\folder\smester 8\skripsi\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD880C4-863B-4B6A-8FC3-E6F4BE7A5862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8C6198-526A-4635-96BF-FED5F328A5AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{80DF3B82-D460-4A33-B933-B48EB543BC7F}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{80DF3B82-D460-4A33-B933-B48EB543BC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
   <si>
     <t>Nama Wisata</t>
   </si>
@@ -137,9 +137,6 @@
     <t xml:space="preserve">pulau sepadan </t>
   </si>
   <si>
-    <t>Atribut</t>
-  </si>
-  <si>
     <t>alam, petualangan, pemandangan, keindahan, habitat, aliran sungai</t>
   </si>
   <si>
@@ -245,9 +242,6 @@
     <t>Air Terjun lubuk mantuk</t>
   </si>
   <si>
-    <t>tempat_id</t>
-  </si>
-  <si>
     <t>Agro Wisata BUKIT BELUAN</t>
   </si>
   <si>
@@ -255,13 +249,16 @@
   </si>
   <si>
     <t>kolam renang, alam, wahana bermain, hoomestay</t>
+  </si>
+  <si>
+    <t>Deskripsi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,27 +267,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -298,14 +308,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -640,511 +667,408 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19894C90-A79F-4811-A2B1-174216E8510D}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.06640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.06640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2">
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3">
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A13">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A14">
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15">
+      <c r="B17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A16">
+      <c r="B18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17">
+      <c r="B20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A18">
+      <c r="B21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19">
+      <c r="B22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20">
+      <c r="B23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" t="s">
-        <v>51</v>
-      </c>
-      <c r="I20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21">
+      <c r="B24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="1">
         <v>24</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="1">
         <v>25</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>53</v>
-      </c>
-      <c r="I22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="1">
         <v>26</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A24">
-        <v>27</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" t="s">
-        <v>55</v>
-      </c>
-      <c r="I24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A25">
-        <v>28</v>
-      </c>
-      <c r="B25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>56</v>
-      </c>
-      <c r="I25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26">
-        <v>29</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" t="s">
-        <v>57</v>
-      </c>
-      <c r="I26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27">
-        <v>30</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="I27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A28">
-        <v>31</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I28">
+      <c r="C29" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A29">
+      <c r="B30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="1">
         <v>34</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" t="s">
-        <v>61</v>
-      </c>
-      <c r="I29">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A30">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" t="s">
-        <v>62</v>
-      </c>
-      <c r="I30">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A31">
-        <v>36</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" t="s">
-        <v>63</v>
-      </c>
-      <c r="I31">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A32">
-        <v>37</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" t="s">
-        <v>64</v>
-      </c>
-      <c r="I32">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A33">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" t="s">
-        <v>65</v>
-      </c>
-      <c r="I33">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A34">
-        <v>39</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" t="s">
-        <v>66</v>
-      </c>
-      <c r="I34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35">
-        <v>40</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" t="s">
-        <v>67</v>
-      </c>
-      <c r="I35">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
-      <c r="I36">
+      <c r="C36" s="1">
         <v>35</v>
       </c>
     </row>
